--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0080.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0080.xlsx
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Bãi Lầy Whining Aix</t>
+          <t>Whining Aix's Mire</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Thành Phố Cảng Guixu</t>
+          <t>Port City of Guixu</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Thành Phố Cảng Guixu</t>
+          <t>Port City of Guixu</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Đồng bằng Trung tâm</t>
+          <t>Central Plains</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Đồng bằng Trung tâm</t>
+          <t>Central Plains</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Rừng Tối</t>
+          <t>Dim Forest</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Rừng Tối</t>
+          <t>Dim Forest</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Hẻm Núi Linh Hồn</t>
+          <t>Gorges of Spirits</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Cao nguyên Desorock</t>
+          <t>Desorock Highland</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Bãi Lầy Whining Aix</t>
+          <t>Whining Aix's Mire</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Bãi Lầy Whining Aix</t>
+          <t>Whining Aix's Mire</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Mt. Pingting</t>
+          <t>Núi Pingting</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>An Toàn Là Trên Hết!</t>
+          <t>An toàn trước đã!</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Weightless Skyscrapers</t>
+          <t>Những Tòa Nhà Trên Mây</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Sky Incinerated</t>
+          <t>Thiên Không Thiêu Rụi</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Thanh Kiếm Chiến Tại Norfall Barrens</t>
+          <t>Lưỡi Kiếm Chiến Tại Norfall Barrens</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Falling Streams</t>
+          <t>Dòng Suối Sa</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Thành Phố Jinzhou</t>
+          <t>Thành phố Jinzhou</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Luminous Petals</t>
+          <t>Cánh Hoa Lấp Lánh</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Vầng Trăng Trong Tầm Tay</t>
+          <t>Trăng Trong Tầm Tay</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Sentinel's Statue</t>
+          <t>Tượng Đấng Sentinel</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Những Giọt Mưa Quá Khứ</t>
+          <t>Giọt Mưa Quá Khứ</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Eternal Blue</t>
+          <t>Xanh Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Daybreak</t>
+          <t>Bình Minh</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Kẻ Thù</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Echoes</t>
+          <t>Echo</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Sceneries</t>
+          <t>Cảnh vật</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Creatures</t>
+          <t>Sinh Vật</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Records</t>
+          <t>Bản ghi</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Main Story</t>
+          <t>Câu Chuyện Chính</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Archives</t>
+          <t>Kho lưu trữ</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Crossing Stars</t>
+          <t>Vượt Biển Sao</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Wildlife</t>
+          <t>Sinh Vật Hoang Dã</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Dishes</t>
+          <t>Món Ăn</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Thuốc</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Vật Liệu</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Vật Liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Vật Liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Vật Liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Vật Liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Vật Liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng cấp Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Vật liệu nâng cấp kỹ năng</t>
+          <t>Vật Liệu Nâng Cấp Kỹ Năng</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Vật liệu nâng cấp kỹ năng</t>
+          <t>Vật Liệu Nâng Cấp Kỹ Năng</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Vật liệu nâng cấp kỹ năng</t>
+          <t>Vật Liệu Nâng Cấp Kỹ Năng</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Tiêu hao</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Tiêu hao</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Tiêu hao</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Nguyên liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Thức ăn</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Nguyên liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Nguyên liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Nguyên liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Nguyên liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Nguyên liệu EXP Vũ khí</t>
+          <t>Vật liệu Tăng EXP Vũ Khí</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Nguyên liệu EXP Vũ khí</t>
+          <t>Vật liệu Tăng EXP Vũ Khí</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Nguyên liệu EXP Vũ khí</t>
+          <t>Vật liệu Tăng EXP Vũ Khí</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Nguyên liệu EXP Vũ khí</t>
+          <t>Vật liệu Tăng EXP Vũ Khí</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Nguyên liệu Thăng hoa Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Nguyên liệu Thăng hoa Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Nguyên liệu Thăng hoa Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Nguyên liệu Thăng hoa Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Nguyên liệu Thăng hoa Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Nguyên liệu Thăng hoa Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Nguyên liệu thăng cấp Vũ khí</t>
+          <t>Vật Liệu Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Discord - Threnodian</t>
+          <t>Tacet Discord - Threnodian</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Discord - Nacrus</t>
+          <t>Tacet Discord - Nacrus</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Discord - Murmur</t>
+          <t>Tacet Discord - Murmur</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Discord - Artifian</t>
+          <t>Tacet Discord - Artifian</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Electro Predator</t>
+          <t>Thú Điện Khát Máu</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Havoc Warrior</t>
+          <t>Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Discord - Murmur</t>
+          <t>Tacet Discord - Murmur</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Discord - Murmur</t>
+          <t>Tacet Discord - Murmur</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Whiff Whaff</t>
+          <t>Phì Phò</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Discord - Murmur</t>
+          <t>Tacet Discord - Murmur</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Discord - Murmur</t>
+          <t>Tacet Discord - Murmur</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Discord - Nacrus</t>
+          <t>Tacet Discord - Nacrus</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Discord - Nacrus</t>
+          <t>Tacet Discord - Nacrus</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Discord - Nacrus</t>
+          <t>Tacet Discord - Nacrus</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Discord - Nacrus</t>
+          <t>Tacet Discord - Nacrus</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Baby Roseshroom</t>
+          <t>Nấm Hồng Bé Nhỏ</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Dân Lưu Đày</t>
+          <t>Dân Lưu Đày Thường</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Exile Commoner (Female)</t>
+          <t>Dân Thường Lưu Đày (Nữ)</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Cryscorpion</t>
+          <t>Bọ Cạp Pha Lê</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Discord - Nacrus</t>
+          <t>Tacet Discord - Nacrus</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Spearback</t>
+          <t>Lưng Lao</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Carapace</t>
+          <t>Vỏ giáp</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Discord - Artifian</t>
+          <t>Tacet Discord - Artifian</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Lãnh Đạo Lưu Đày</t>
+          <t>Thủ Lĩnh Lưu Đày</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Exile Technician</t>
+          <t>Kỹ Sư Lưu Đày</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Fractsidus Executioner</t>
+          <t>Đao Phủ Fractsidus</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Discord - Calamon</t>
+          <t>Tacet Discord - Calamon</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Discord - Threnodian</t>
+          <t>Tacet Discord - Threnodian</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Discord - Natural Kind</t>
+          <t>Tacet Discord - Bản Chất Tự Nhiên</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Discord - Natural Kind</t>
+          <t>Tacet Discord - Bản Chất Tự Nhiên</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Electro Predator</t>
+          <t>Thú Điện Khát Máu</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Havoc Warrior</t>
+          <t>Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Discord-Murmurin</t>
+          <t>Tacet Discord - Murmurin</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Discord-Murmurin</t>
+          <t>Tacet Discord - Murmurin</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Whiff Whaff</t>
+          <t>Phì Phò</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Discord-Murmurin</t>
+          <t>Tacet Discord - Murmurin</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Whiff Whaff</t>
+          <t>Phì Phò</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Discord-Murmurin</t>
+          <t>Tacet Discord - Murmurin</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
